--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Bergström, Suvi Bergström</t>
+          <t>Suvi Bergström, Stefan Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19015-2026 artfynd.xlsx
+++ b/artfynd/A 19015-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136077179</v>
       </c>
       <c r="B2" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
